--- a/task/关键标准答案.xlsx
+++ b/task/关键标准答案.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="R450d90b48e294295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="R23a745b985684027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rd1aca477e3cf47cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="R007636f87708476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="R2bff7ba47d284f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="交付物答案清单" sheetId="1" r:id="Rc1810e7849164199"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定字段答案" sheetId="2" r:id="Rdbef2dc15d174f00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定集合答案" sheetId="3" r:id="Rbad249a24e02449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="固定数值答案" sheetId="4" r:id="Rff758d72134f4bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="允许变体答案" sheetId="5" r:id="Rc9df4d9f32cd42a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -424,7 +424,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7fd5a85b91649b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad026b43fbd5461a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1660,7 +1660,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7a051b3e72e414c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9b8ca7afd4c4aed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1700,7 +1700,7 @@
         <x:v>output/support_sla_repaired.db|output/sql/rebuild_sla.sql|output/reports/sla_clock.csv|output/reports/pause_interval_audit.csv|output/reports/breach_queue.csv</x:v>
       </x:c>
       <x:c r="D2" s="7" t="str">
-        <x:v>任务交付合同</x:v>
+        <x:v>与任务指定的交付路径一致</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="86" customHeight="1">
@@ -1708,13 +1708,13 @@
         <x:v>输入数据包</x:v>
       </x:c>
       <x:c r="B3" s="7" t="str">
-        <x:v>开工材料集合</x:v>
+        <x:v>业务材料集合</x:v>
       </x:c>
       <x:c r="C3" s="7" t="str">
         <x:v>input_data/README.md|input_data/business_calendar.json|input_data/package.json|input_data/starter/rebuild_sla.sql|input_data/support_sla.db|input_data/tools/run-task.mjs</x:v>
       </x:c>
       <x:c r="D3" s="7" t="str">
-        <x:v>入口实际读取与业务开工材料</x:v>
+        <x:v>入口读取的工单库、业务日历、SQL和启动材料</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="86" customHeight="1">
@@ -1790,7 +1790,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R802ce87724eb4ab0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c2ee9bf265244bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2530,7 +2530,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafb453d2f33446ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5fe7164922c478b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2632,7 +2632,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47717dd863644239"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a7dc3fa9467438b"/>
   </x:tableParts>
 </x:worksheet>
 </file>